--- a/src/source/table1.xlsx
+++ b/src/source/table1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -380,18 +380,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -808,7 +802,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -832,16 +826,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -850,85 +844,85 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -981,13 +975,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1020,10 +1014,10 @@
     <xf numFmtId="58" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1346,13 +1340,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="3.75" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.75454545454545" style="2" customWidth="1"/>
     <col min="2" max="2" width="15.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="2" customWidth="1"/>
-    <col min="4" max="8" width="11.875" style="2" customWidth="1"/>
-    <col min="9" max="10" width="11.25" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.6272727272727" style="2" customWidth="1"/>
+    <col min="4" max="8" width="11.8727272727273" style="2" customWidth="1"/>
+    <col min="9" max="10" width="11.2545454545455" style="2" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
